--- a/data/sce_compartment_curation/mitochondrial_inner_membrane_annotations_manual_v2.xlsx
+++ b/data/sce_compartment_curation/mitochondrial_inner_membrane_annotations_manual_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YEL020W-A</t>
+          <t>YJL062W-A</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YJR045C</t>
+          <t>YPL271W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YKR042W</t>
+          <t>YOR065W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YPL132W</t>
+          <t>YLR295C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YLR295C</t>
+          <t>YPL063W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YLL041C</t>
+          <t>YER017C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YGL080W</t>
+          <t>YML110C</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YLR393W</t>
+          <t>YOR176W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YKR087C</t>
+          <t>YGR033C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YML129C</t>
+          <t>YBR039W</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YKL016C</t>
+          <t>YPL134C</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YLR251W</t>
+          <t>YDR393W</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YPL134C</t>
+          <t>YGR096W</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YPR140W</t>
+          <t>YBL099W</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YDL217C</t>
+          <t>YPR140W</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YER014W</t>
+          <t>YBR044C</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YPL103C</t>
+          <t>YOR147W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YDL174C</t>
+          <t>YOR205C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YDR119W-A</t>
+          <t>YNR040W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YDR079W</t>
+          <t>YPL099C</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YOL096C</t>
+          <t>YOL027C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YPL078C</t>
+          <t>YOL096C</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YNR045W</t>
+          <t>YPL132W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YBR039W</t>
+          <t>YML081C-A</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YKL120W</t>
+          <t>YGR231C</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q0130</t>
+          <t>YJR045C</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YGR255C</t>
+          <t>YML030W</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YDR298C</t>
+          <t>YJL143W</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YOR297C</t>
+          <t>YJL208C</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YPL109C</t>
+          <t>YLR251W</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YGR101W</t>
+          <t>YMR301C</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YNR017W</t>
+          <t>YPL078C</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YGR112W</t>
+          <t>YOR232W</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YER170W</t>
+          <t>YDR204W</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YHR199C</t>
+          <t>YOR037W</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YFR045W</t>
+          <t>YER141W</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YLR164W</t>
+          <t>YDR322C-A</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YLR203C</t>
+          <t>YDR236C</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YDL183C</t>
+          <t>YNR045W</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YJL166W</t>
+          <t>YOL077W-A</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YOR266W</t>
+          <t>YDR178W</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YLR283W</t>
+          <t>YGR222W</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YOR222W</t>
+          <t>YJR121W</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YOL077W-A</t>
+          <t>YER014W</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YIL022W</t>
+          <t>YLR193C</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YDL069C</t>
+          <t>YMR257C</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YDL027C</t>
+          <t>YGR110W</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YER153C</t>
+          <t>YCL044C</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YMR056C</t>
+          <t>YEL020W-A</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YBL095W</t>
+          <t>YIR024C</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YOR232W</t>
+          <t>YBL030C</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YDR204W</t>
+          <t>YER153C</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YER017C</t>
+          <t>YPR020W</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YDR376W</t>
+          <t>YLR283W</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YMR098C</t>
+          <t>YDR350C</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YOR037W</t>
+          <t>YDR282C</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YJL054W</t>
+          <t>YDR377W</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YOR125C</t>
+          <t>YBR185C</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YIL154C</t>
+          <t>YGR132C</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YKR016W</t>
+          <t>YGR183C</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YDR377W</t>
+          <t>YDL174C</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YEL024W</t>
+          <t>YGL080W</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YPL099C</t>
+          <t>YFL046W</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YMR150C</t>
+          <t>YKL120W</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YHR162W</t>
+          <t>YMR302C</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YBL045C</t>
+          <t>YEL024W</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YHR002W</t>
+          <t>YMR056C</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YNR018W</t>
+          <t>YPR125W</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YLR008C</t>
+          <t>YOR222W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YPL270W</t>
+          <t>YDL027C</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YOR205C</t>
+          <t>YLR139C</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q0080</t>
+          <t>YOR297C</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YBR037C</t>
+          <t>YLR393W</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YDR381C-A</t>
+          <t>YDR376W</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YDR282C</t>
+          <t>YMR115W</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YJL208C</t>
+          <t>YPL060W</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YGR110W</t>
+          <t>YLR203C</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YDR178W</t>
+          <t>YMR098C</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YML030W</t>
+          <t>YNR017W</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YDR375C</t>
+          <t>YOL008W</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YHR168W</t>
+          <t>YDR381C-A</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YML110C</t>
+          <t>YEL052W</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YEL059C-A</t>
+          <t>YHR199C</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YJR034W</t>
+          <t>YNL169C</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YIR024C</t>
+          <t>YNR018W</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YJR077C</t>
+          <t>YHR198C</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YKR052C</t>
+          <t>Q0130</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Q0085</t>
+          <t>YHR168W</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YHR194W</t>
+          <t>YBL045C</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YJL003W</t>
+          <t>YDL183C</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YLR067C</t>
+          <t>YGR101W</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YLR139C</t>
+          <t>YFR033C</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YMR257C</t>
+          <t>YKR087C</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YOR334W</t>
+          <t>YLR008C</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YML081C-A</t>
+          <t>YIL157C</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YPL060W</t>
+          <t>YPR061C</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YFR033C</t>
+          <t>YDR298C</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YJR121W</t>
+          <t>YGR062C</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YDR529C</t>
+          <t>YJR080C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YMR302C</t>
+          <t>YJL003W</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YDR236C</t>
+          <t>YBR037C</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YMR089C</t>
+          <t>Q0080</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YKL195W</t>
+          <t>YPR024W</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YBR085W</t>
+          <t>YKL195W</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YPR061C</t>
+          <t>YMR089C</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YBL030C</t>
+          <t>YJL104W</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YGR096W</t>
+          <t>YPR191W</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YLR201C</t>
+          <t>YIL154C</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YPR020W</t>
+          <t>YGR112W</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YFL046W</t>
+          <t>YMR023C</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YDR322C-A</t>
+          <t>YIL022W</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YOR176W</t>
+          <t>YBR085W</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YGR062C</t>
+          <t>YDL004W</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YGR183C</t>
+          <t>YDL217C</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YPL063W</t>
+          <t>YMR166C</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YPR191W</t>
+          <t>YDL069C</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YOR100C</t>
+          <t>YDR375C</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YDR350C</t>
+          <t>YLR067C</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YJR080C</t>
+          <t>YBR091C</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YDL004W</t>
+          <t>YJL054W</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YGR231C</t>
+          <t>YHR194W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YNL169C</t>
+          <t>YKR016W</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YKL141W</t>
+          <t>YDR119W-A</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YMR115W</t>
+          <t>YOR100C</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YOR147W</t>
+          <t>YML129C</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Q0105</t>
+          <t>YPL109C</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YGR132C</t>
+          <t>YKR052C</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YMR038C</t>
+          <t>YLR201C</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YPR024W</t>
+          <t>YOR211C</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YBR044C</t>
+          <t>YOR334W</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YKL148C</t>
+          <t>YHR001W-A</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YPR125W</t>
+          <t>YKL141W</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YJL143W</t>
+          <t>YER170W</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YOL008W</t>
+          <t>YJR034W</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YBR091C</t>
+          <t>YLR204W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YHR198C</t>
+          <t>YLL041C</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YOR065W</t>
+          <t>YGR255C</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YMR166C</t>
+          <t>YFR045W</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YBR185C</t>
+          <t>YPL103C</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YLR193C</t>
+          <t>Q0085</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YGR222W</t>
+          <t>YHR005C-A</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YNL328C</t>
+          <t>YPL270W</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YER141W</t>
+          <t>YDR529C</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YLR204W</t>
+          <t>YLR164W</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YKL011C</t>
+          <t>YDR231C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YGR033C</t>
+          <t>YHR002W</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YMR097C</t>
+          <t>YOR266W</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YDR231C</t>
+          <t>YOR125C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YPL271W</t>
+          <t>YMR038C</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YHR005C-A</t>
+          <t>Q0105</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YIL157C</t>
+          <t>YNL328C</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YLR188W</t>
+          <t>YJR077C</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YEL052W</t>
+          <t>YLR188W</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YOL027C</t>
+          <t>YKR042W</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YJL062W-A</t>
+          <t>YLR077W</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YNR040W</t>
+          <t>YKL011C</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YDR393W</t>
+          <t>YPR011C</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YOR211C</t>
+          <t>YMR150C</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YJL104W</t>
+          <t>YKL148C</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YLR253W</t>
+          <t>YHR162W</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YHR001W-A</t>
+          <t>YKL016C</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YPR011C</t>
+          <t>YLR253W</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YBL099W</t>
+          <t>YDR079W</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YCL044C</t>
+          <t>YJL166W</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YLR077W</t>
+          <t>YEL059C-A</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YMR023C</t>
+          <t>YBL095W</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YMR301C</t>
+          <t>YMR097C</t>
         </is>
       </c>
     </row>
